--- a/原型页面清单.xlsx
+++ b/原型页面清单.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>智慧水务高保真原型 · 页面清单（2026-10-09 共 35 页）</t>
+          <t>智慧水务高保真原型 · 页面清单（2026-10-09 共 34 页）</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>档案管理</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>表具类型</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/archive/meter-type.html</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>户表管理</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>用户开户</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/meter/user-open.html</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>用户开户</t>
+          <t>用户换表</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/meter/user-open.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/meter/user-change.html</t>
         </is>
       </c>
     </row>
@@ -698,46 +698,46 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>用户换表</t>
+          <t>用户销户</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/meter/user-change.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/meter/user-close.html</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>户表管理</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>用户销户</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/meter/user-close.html</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>抄表管理</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>4G NB抄表</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/reading/4g-nb.html</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>抄表管理</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>4G NB抄表</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/reading/4g-nb.html</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>收费管理</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>综合缴费</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/payment/payment-main.html</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>综合缴费</t>
+          <t>缴费记录</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/payment/payment-main.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/payment/payment-record.html</t>
         </is>
       </c>
     </row>
@@ -766,29 +766,29 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>缴费记录</t>
+          <t>纠正异常</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/payment/payment-record.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/payment/correct-abnormal.html</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>收费管理</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>纠正异常</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/payment/correct-abnormal.html</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>报表分析</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>余额不足统计</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-balance.html</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>余额不足统计</t>
+          <t>周期账单表</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-balance.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-bill-cycle.html</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>周期账单表</t>
+          <t>关阀户表统计</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-bill-cycle.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-valve-meter.html</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>关阀户表统计</t>
+          <t>价格计费统计</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-valve-meter.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-price.html</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>价格计费统计</t>
+          <t>报停复开记录</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-price.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-stop-record.html</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>报停复开记录</t>
+          <t>关阀用水用户稽查</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-stop-record.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-valve-user.html</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>关阀用水用户稽查</t>
+          <t>户内漏水预警稽查</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-valve-user.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-leak.html</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>户内漏水预警稽查</t>
+          <t>未上报统计表</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-leak.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-unreported.html</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>未上报统计表</t>
+          <t>用户缴费汇总表</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-unreported.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-pay-summary.html</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>用户缴费汇总表</t>
+          <t>销户记录表</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-pay-summary.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-close-record.html</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>销户记录表</t>
+          <t>欠费用户查询</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-close-record.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-arrears.html</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>欠费用户查询</t>
+          <t>报停费用汇总</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-arrears.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-stop-fee.html</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>报停费用汇总</t>
+          <t>用户缴费明细表</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-stop-fee.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-pay-detail.html</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>用户缴费明细表</t>
+          <t>抄表记录表</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-pay-detail.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-reading-record.html</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>抄表记录表</t>
+          <t>命令记录表</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-reading-record.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-cmd-record.html</t>
         </is>
       </c>
     </row>
@@ -1038,46 +1038,46 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>命令记录表</t>
+          <t>换表记录表</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-cmd-record.html</t>
+          <t>https://ifashion2016.github.io/water-prototype/report/stat-change-record.html</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>报表分析</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>换表记录表</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/report/stat-change-record.html</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>功能配置</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>微信配置 + 表具类型</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/config/config-wechat-meter.html</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>功能配置</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>微信配置 + 表具类型</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/config/config-wechat-meter.html</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>网上营业厅</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>移动缴费网厅（PC）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>https://ifashion2016.github.io/water-prototype/online/online-pc.html</t>
         </is>
       </c>
     </row>
@@ -1089,27 +1089,10 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>移动缴费网厅（PC）</t>
+          <t>移动缴费H5（移动端）</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>https://ifashion2016.github.io/water-prototype/online/online-pc.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>网上营业厅</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>移动缴费H5（移动端）</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>https://ifashion2016.github.io/water-prototype/online/online-h5.html</t>
         </is>
@@ -1154,7 +1137,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
